--- a/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
+++ b/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
@@ -30,12 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="500">
   <si>
     <t xml:space="preserve">CGI-GAP-001 — NIST CSF 2.0 Gap Assessment &amp; Maturity Scorecard v1.0</t>
   </si>
   <si>
-    <t xml:space="preserve">FICTIONAL DATA. Cypher Group Inc. is a fictional company. Every finding, score and figure was created to demonstrate applied GRC methodology.</t>
+    <t xml:space="preserve">SIMULATED CASE STUDY. Cypher Group Inc. is a simulated company. Every finding, score and figure was created to demonstrate applied GRC methodology.</t>
   </si>
   <si>
     <t xml:space="preserve">Scope</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">A compromise at AWS, GitHub or Google Workspace would reach all customer data with no contractual remedy, no assessed control baseline and no notification pathway; enterprise buyers treat a missing vendor register as a hard fail.</t>
   </si>
   <si>
-    <t xml:space="preserve">Build a tiered vendor inventory covering AWS, GitHub, Slack, Google Workspace and Stripe with data classification exposure, collect each provider's assurance artifact and DPA, and add permitted third-party destinations to CGI-POL-004 §4.2. (Delivered as Project 4.)</t>
+    <t xml:space="preserve">Build a tiered vendor inventory covering AWS, GitHub, Slack, Google Workspace and Stripe with data classification exposure, collect each provider's assurance artifact and DPA, and add permitted third-party destinations to CGI-POL-004 §4.2. (Delivered 15 Sep 2026 as Project 4 (CGI-TPR-001), three quarters ahead of its Q2 2027 slot.)</t>
   </si>
   <si>
     <t xml:space="preserve">M</t>
@@ -1235,7 +1235,10 @@
     <t xml:space="preserve">GV.SC</t>
   </si>
   <si>
-    <t xml:space="preserve">The only Category scored zero that is also a hard commercial blocker: enterprise buyers treat a missing vendor register as an immediate fail. Delivered as Project 4.</t>
+    <t xml:space="preserve">The only Category scored zero that is also a hard commercial blocker: enterprise buyers treat a missing vendor register as an immediate fail. Delivered 15 Sep 2026 as Project 4 (CGI-TPR-001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> three quarters ahead of its Q2 2027 slot.</t>
   </si>
   <si>
     <t xml:space="preserve">REC-16</t>
@@ -1520,7 +1523,7 @@
     <t xml:space="preserve">Tables contain one value per cell and no merged cells</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional-data notice present if this is a portfolio scenario</t>
+    <t xml:space="preserve">Case-study notice present if this is a portfolio scenario</t>
   </si>
   <si>
     <t xml:space="preserve">Control gap IDs match CGI-RSK-001 §4.3 exactly (CG-01 to CG-05)</t>
@@ -2064,7 +2067,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>NIST CSF 2.0 maturity — current vs target (fictional)</a:t>
+              <a:t>NIST CSF 2.0 maturity — current vs target (simulated)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2297,11 +2300,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="45648483"/>
-        <c:axId val="20534892"/>
+        <c:axId val="69650005"/>
+        <c:axId val="5331733"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="45648483"/>
+        <c:axId val="69650005"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2330,7 +2333,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20534892"/>
+        <c:crossAx val="5331733"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2338,7 +2341,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20534892"/>
+        <c:axId val="5331733"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="4"/>
@@ -2382,7 +2385,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45648483"/>
+        <c:crossAx val="69650005"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
@@ -4580,7 +4583,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5218,16 +5221,19 @@
       <c r="L16" s="13" t="s">
         <v>401</v>
       </c>
+      <c r="M16" s="13" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>349</v>
@@ -5236,7 +5242,7 @@
         <v>104</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>5</v>
@@ -5249,27 +5255,27 @@
         <v>136</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>182</v>
@@ -5288,24 +5294,24 @@
         <v>136</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>375</v>
@@ -5327,43 +5333,43 @@
         <v>164</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>322</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D23" s="16" t="n">
         <f aca="false">COUNTIF(J2:J19,"Q4 2026")</f>
@@ -5372,13 +5378,13 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>344</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D24" s="16" t="n">
         <f aca="false">COUNTIF(J2:J19,"Q1 2027")</f>
@@ -5387,13 +5393,13 @@
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>376</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D25" s="16" t="n">
         <f aca="false">COUNTIF(J2:J19,"Q2 2027")</f>
@@ -5402,13 +5408,13 @@
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D26" s="16" t="n">
         <f aca="false">COUNTIF(J2:J19,"Q3 2027")+COUNTIF(J2:J19,"Q4 2027")</f>
@@ -5465,31 +5471,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B5" s="16" t="n">
         <f aca="false">COUNTA(02_Assessment!A2:A23)</f>
@@ -5505,7 +5511,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">SUMPRODUCT((03_Heatmap!B5:B10&gt;0)*1)</f>
@@ -5521,7 +5527,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUM(02_Assessment!G2:G23)</f>
@@ -5537,7 +5543,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">SUM(02_Assessment!H2:H23)</f>
@@ -5553,7 +5559,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B9" s="16" t="n">
         <f aca="false">COUNTIF(02_Assessment!H2:H23,3)</f>
@@ -5569,7 +5575,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">COUNTIF(02_Assessment!H2:H23,2)</f>
@@ -5585,7 +5591,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">COUNTIF(02_Assessment!H2:H23,4)</f>
@@ -5601,7 +5607,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">SUMPRODUCT((02_Assessment!H2:H23&lt;02_Assessment!G2:G23)*1)</f>
@@ -5617,7 +5623,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">SUMPRODUCT((02_Assessment!I2:I23&lt;&gt;02_Assessment!H2:H23-02_Assessment!G2:G23)*1)</f>
@@ -5633,7 +5639,7 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">SUMPRODUCT((02_Assessment!G2:G23&gt;=3)*((ISNUMBER(SEARCH("R-004",02_Assessment!J2:J23)))+(ISNUMBER(SEARCH("R-005",02_Assessment!J2:J23)))&gt;0))</f>
@@ -5649,7 +5655,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">INDEX(02_Assessment!G2:G23,MATCH("PR.PS*",02_Assessment!C2:C23,0))</f>
@@ -5665,7 +5671,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">INDEX(02_Assessment!G2:G23,MATCH("PR.IR*",02_Assessment!C2:C23,0))</f>
@@ -5681,7 +5687,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">COUNTIFS(02_Assessment!G2:G23,0,02_Assessment!F2:F23,"*fragment*")</f>
@@ -5697,7 +5703,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">COUNTA(04_Roadmap!A2:A19)</f>
@@ -5713,7 +5719,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">ROUND(03_Heatmap!C11,2)</f>
@@ -5729,7 +5735,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">ROUND(03_Heatmap!D11,2)</f>
@@ -5745,38 +5751,38 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>330</v>
@@ -5784,10 +5790,10 @@
     </row>
     <row r="25" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>349</v>
@@ -5796,32 +5802,32 @@
         <v>46</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>364</v>
@@ -5835,19 +5841,19 @@
     </row>
     <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -5885,16 +5891,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5902,10 +5908,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D2" s="13"/>
     </row>
@@ -5914,10 +5920,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>486</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>485</v>
       </c>
       <c r="D3" s="13"/>
     </row>
@@ -5926,10 +5932,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D4" s="13"/>
     </row>
@@ -5938,10 +5944,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D5" s="13"/>
     </row>
@@ -5950,10 +5956,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D6" s="13"/>
     </row>
@@ -5962,10 +5968,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D7" s="13"/>
     </row>
@@ -5974,10 +5980,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D8" s="13"/>
     </row>
@@ -5986,10 +5992,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D9" s="13"/>
     </row>
@@ -5998,10 +6004,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D10" s="13"/>
     </row>
@@ -6010,10 +6016,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D11" s="13"/>
     </row>
@@ -6022,10 +6028,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D12" s="13"/>
     </row>
@@ -6034,10 +6040,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D13" s="13"/>
     </row>
@@ -6046,10 +6052,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D14" s="13"/>
     </row>
@@ -6058,10 +6064,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D15" s="13"/>
     </row>

--- a/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
+++ b/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
@@ -143,13 +143,13 @@
     <t xml:space="preserve">PUBLISHING</t>
   </si>
   <si>
-    <t xml:space="preserve">GitHub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload this .xlsx next to its .md file. GitHub cannot preview .xlsx, so the project README links to it as a download.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notion</t>
+    <t xml:space="preserve">CodeCo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload this .xlsx next to its .md file. CodeCo cannot preview .xlsx, so the project README links to it as a download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WikiCo</t>
   </si>
   <si>
     <t xml:space="preserve">Import the matching CSV files from the data/ folder (Settings → Import → CSV) for sortable databases.</t>
@@ -479,16 +479,16 @@
     <t xml:space="preserve">Cyber supply chain risk management processes are identified, established, managed, monitored and improved by organizational stakeholders.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nothing exists in this Category beyond two fragments. Cypher Group Inc. runs its production stack on five known third parties - AWS for hosting, GitHub for source code, Slack for communications, Google Workspace for email and documents and Stripe for payment metadata - and none has been security-assessed, none has a recorded assurance artifact such as a SOC 2 report or ISO 27001 certificate on file, and no data processing agreements are tracked in a register. CGI-POL-004 §4.2 Handling Matrix specifies how classified data must be handled but names no permitted or prohibited third-party destinations, so a Confidential record may be pasted into an unvetted SaaS tool without breaching any written rule. The two fragments are CGI-POL-001 §4.6.1, which requires CTO approval before any new third-party service is used, and CGI-POL-003 §4.6, which requires a named sponsor and an expiry date for third-party user access. Neither has an inventory, a tiering rule, an assessment method or an execution record behind it, so under the fragment rule in §3.1 the Category stays at 0. This Category is also entirely outside the scope of CGI-RSK-001, which assessed no supplier-originated scenario.</t>
+    <t xml:space="preserve">Nothing exists in this Category beyond two fragments. Cypher Group Inc. runs its production stack on five known third parties - CloudCo for hosting, CodeCo for source code, ChatCo for communications, OfficeCo for email and documents and PaymentsCo for payment metadata - and none has been security-assessed, none has a recorded assurance artifact such as a SOC 2 report or ISO 27001 certificate on file, and no data processing agreements are tracked in a register. CGI-POL-004 §4.2 Handling Matrix specifies how classified data must be handled but names no permitted or prohibited third-party destinations, so a Confidential record may be pasted into an unvetted SaaS tool without breaching any written rule. The two fragments are CGI-POL-001 §4.6.1, which requires CTO approval before any new third-party service is used, and CGI-POL-003 §4.6, which requires a named sponsor and an expiry date for third-party user access. Neither has an inventory, a tiering rule, an assessment method or an execution record behind it, so under the fragment rule in §3.1 the Category stays at 0. This Category is also entirely outside the scope of CGI-RSK-001, which assessed no supplier-originated scenario.</t>
   </si>
   <si>
     <t xml:space="preserve">No vendor inventory on file; CGI-POL-004 §4.2 (no third-party destinations named); CGI-POL-001 §4.6.1 and CGI-POL-003 §4.6 (fragments only); CGI-RSK-001 scope statement</t>
   </si>
   <si>
-    <t xml:space="preserve">A compromise at AWS, GitHub or Google Workspace would reach all customer data with no contractual remedy, no assessed control baseline and no notification pathway; enterprise buyers treat a missing vendor register as a hard fail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a tiered vendor inventory covering AWS, GitHub, Slack, Google Workspace and Stripe with data classification exposure, collect each provider's assurance artifact and DPA, and add permitted third-party destinations to CGI-POL-004 §4.2. (Delivered 15 Sep 2026 as Project 4 (CGI-TPR-001), three quarters ahead of its Q2 2027 slot.)</t>
+    <t xml:space="preserve">A compromise at CloudCo, CodeCo or OfficeCo would reach all customer data with no contractual remedy, no assessed control baseline and no notification pathway; enterprise buyers treat a missing vendor register as a hard fail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a tiered vendor inventory covering CloudCo, CodeCo, ChatCo, OfficeCo and PaymentsCo with data classification exposure, collect each provider's assurance artifact and DPA, and add permitted third-party destinations to CGI-POL-004 §4.2. (Delivered 15 Sep 2026 as Project 4 (CGI-TPR-001), three quarters ahead of its Q2 2027 slot.)</t>
   </si>
   <si>
     <t xml:space="preserve">M</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">Assets - data, hardware, software, systems, facilities, services and people - that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to organizational objectives and the organization's risk strategy.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-004 establishes a four-tier data classification scheme with a §4.2 Handling Matrix and a §4.1.3 aggregation rule, so Cypher Group Inc. knows what its data is worth in principle, but there is no inventory recording where any of it actually lives. No list exists of AWS accounts and their S3 buckets and RDS instances, GitHub repositories, Google Workspace shared drives, Slack channels or Stripe objects, and no endpoint register exists for the 50 staff devices governed by CGI-POL-001 §4.4 BYOD. The classification scheme is therefore unapplied: no asset carries a classification label, which means the Handling Matrix cannot be enforced or audited against anything.</t>
+    <t xml:space="preserve">CGI-POL-004 establishes a four-tier data classification scheme with a §4.2 Handling Matrix and a §4.1.3 aggregation rule, so Cypher Group Inc. knows what its data is worth in principle, but there is no inventory recording where any of it actually lives. No list exists of CloudCo accounts and their S3 buckets and RDS instances, CodeCo repositories, OfficeCo shared drives, ChatCo channels or PaymentsCo objects, and no endpoint register exists for the 50 staff devices governed by CGI-POL-001 §4.4 BYOD. The classification scheme is therefore unapplied: no asset carries a classification label, which means the Handling Matrix cannot be enforced or audited against anything.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-POL-004 §4.1 to §4.2; CGI-POL-001 §4.4 (BYOD, no device register); no asset inventory on file</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">You cannot protect, monitor, review access to or restore an asset you have not recorded; the absence of an inventory is the root blocker under access review, cloud hardening, monitoring and recovery alike.</t>
   </si>
   <si>
-    <t xml:space="preserve">Build an asset and SaaS inventory covering AWS accounts and data stores, GitHub repositories, Google Workspace shared drives, Slack workspaces, Stripe objects and staff endpoints, and apply a CGI-POL-004 classification label to every entry.</t>
+    <t xml:space="preserve">Build an asset and SaaS inventory covering CloudCo accounts and data stores, CodeCo repositories, OfficeCo shared drives, ChatCo workspaces, PaymentsCo objects and staff endpoints, and apply a CGI-POL-004 classification label to every entry.</t>
   </si>
   <si>
     <t xml:space="preserve">IT Operations Manager</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">Data is managed consistent with the organization's risk strategy to protect the confidentiality, integrity and availability of information.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-004 gives Cypher Group Inc. a well-built classification foundation - four tiers, a §4.2 Handling Matrix, a §4.1.3 aggregation rule and the §4.1.4 decision to hold no cardholder numbers, formalised as the avoidance AVD-001, which is a genuine architectural risk reduction rather than a paper control. Beyond classification the Category is unimplemented: no encryption standard names required algorithms or key management for data at rest in AWS or in transit, no retention or secure deletion schedule has been executed, and no data loss prevention or egress monitoring exists on Google Workspace or GitHub, which CGI-RSK-001 records as control gap CG-05 and which is the reason R-003 retains a residual score of 6 despite the JML controls in CGI-POL-003.</t>
+    <t xml:space="preserve">CGI-POL-004 gives Cypher Group Inc. a well-built classification foundation - four tiers, a §4.2 Handling Matrix, a §4.1.3 aggregation rule and the §4.1.4 decision to hold no cardholder numbers, formalised as the avoidance AVD-001, which is a genuine architectural risk reduction rather than a paper control. Beyond classification the Category is unimplemented: no encryption standard names required algorithms or key management for data at rest in CloudCo or in transit, no retention or secure deletion schedule has been executed, and no data loss prevention or egress monitoring exists on OfficeCo or CodeCo, which CGI-RSK-001 records as control gap CG-05 and which is the reason R-003 retains a residual score of 6 despite the JML controls in CGI-POL-003.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-POL-004 §4.1.3, §4.1.4, §4.2; AVD-001; CGI-RSK-001 CG-05</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">Classified data can leave the organisation through an ordinary download or repository clone with no technical barrier and no record that it happened, making the insider scenario R-003 undetectable rather than merely unprevented.</t>
   </si>
   <si>
-    <t xml:space="preserve">Publish an encryption standard covering AWS data at rest and in transit with named algorithms and key management, define and execute a retention and secure deletion schedule, and deploy data egress monitoring on Google Workspace and GitHub.</t>
+    <t xml:space="preserve">Publish an encryption standard covering CloudCo data at rest and in transit with named algorithms and key management, define and execute a retention and secure deletion schedule, and deploy data egress monitoring on OfficeCo and CodeCo.</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.12 Classification of information; A.5.14 Information transfer; A.8.10 Information deletion; A.8.11 Data masking; A.8.12 Data leakage prevention; A.8.24 Use of cryptography</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">The hardware, software and services of physical and virtual platforms are managed consistent with the organization's risk strategy to protect their confidentiality, integrity and availability.</t>
   </si>
   <si>
-    <t xml:space="preserve">This Category scores zero and shares the largest gap in the assessment with PR.IR. Cypher Group Inc. builds and ships a B2B SaaS product from GitHub to AWS with no secure development lifecycle whatsoever: no secure development or change management policy exists, CGI-POL-007 having been recommended in CGI-RSK-001 but never written; there is no mandatory peer code review, no branch protection on the repositories holding production code, no separation of development and production environments on record, and no application security testing. There is equally no vulnerability management for the platform: no scanning, no severity-based remediation SLA and no server configuration baseline, with CGI-POL-008 likewise recommended and unwritten. CGI-RSK-001 records both halves as control gap CG-02. Two fragments exist and were weighed: CGI-POL-001 §4.4.3 requires endpoint operating-system and browser patches within 14 days, and CGI-POL-002 §4.5.2 requires GitHub secret scanning and push protection. Neither governs how code is reviewed, tested or released, so under the fragment rule in §3.1 the Category stays at 0. The entire Project 1 policy pack contains no clause governing how code reaches production, which is precisely why R-004 remains at residual High.</t>
+    <t xml:space="preserve">This Category scores zero and shares the largest gap in the assessment with PR.IR. Cypher Group Inc. builds and ships a B2B SaaS product from CodeCo to CloudCo with no secure development lifecycle whatsoever: no secure development or change management policy exists, CGI-POL-007 having been recommended in CGI-RSK-001 but never written; there is no mandatory peer code review, no branch protection on the repositories holding production code, no separation of development and production environments on record, and no application security testing. There is equally no vulnerability management for the platform: no scanning, no severity-based remediation SLA and no server configuration baseline, with CGI-POL-008 likewise recommended and unwritten. CGI-RSK-001 records both halves as control gap CG-02. Two fragments exist and were weighed: CGI-POL-001 §4.4.3 requires endpoint operating-system and browser patches within 14 days, and CGI-POL-002 §4.5.2 requires CodeCo secret scanning and push protection. Neither governs how code is reviewed, tested or released, so under the fragment rule in §3.1 the Category stays at 0. The entire Project 1 policy pack contains no clause governing how code reaches production, which is precisely why R-004 remains at residual High.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-RSK-001 CG-02; CGI-POL-007 and CGI-POL-008 recommended, not written; CGI-POL-001 §4.4.3 and CGI-POL-002 §4.5.2 (fragments only); no branch protection or scan evidence on file</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">R-004 (production API authorisation flaw) stays at residual 12, High, after treatment because no control in the policy pack touches the code path; an authorisation defect can reach approximately 200 customers' data with nothing standing between the commit and production.</t>
   </si>
   <si>
-    <t xml:space="preserve">Publish CGI-POL-007 and enforce GitHub branch protection with mandatory peer review and no direct commits to main; publish CGI-POL-008 and begin authenticated vulnerability scanning with severity-based remediation SLAs.</t>
+    <t xml:space="preserve">Publish CGI-POL-007 and enforce CodeCo branch protection with mandatory peer review and no direct commits to main; publish CGI-POL-008 and begin authenticated vulnerability scanning with severity-based remediation SLAs.</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.8 Management of technical vulnerabilities; A.8.9 Configuration management; A.8.25 Secure development life cycle; A.8.28 Secure coding; A.8.29 Security testing in development and acceptance; A.8.31 Separation of development, test and production environments; A.8.32 Change management</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">Security architectures are managed with the organization's risk strategy to protect asset confidentiality, integrity and availability, and organizational resilience.</t>
   </si>
   <si>
-    <t xml:space="preserve">This Category also scores zero. There is no documented AWS configuration baseline, no benchmark such as CIS AWS Foundations has been applied, no continuous cloud security posture monitoring is enabled, and no network segmentation or production access boundary is recorded anywhere - collectively control gap CG-03 in CGI-RSK-001. Backups exist as AWS native snapshots but no restore has ever been tested and no RTO or RPO has been declared, so the company holds a backup but has never demonstrated a recovery capability; CGI-POL-006 Backup and Recovery was recommended in CGI-RSK-001 and has not been written (control gap CG-01). No policy in the CGI-POL-001 to CGI-POL-005 pack addresses cloud configuration at all, which is the documented reason R-005 remains at residual High.</t>
+    <t xml:space="preserve">This Category also scores zero. There is no documented CloudCo configuration baseline, no benchmark such as CIS CloudCo Foundations has been applied, no continuous cloud security posture monitoring is enabled, and no network segmentation or production access boundary is recorded anywhere - collectively control gap CG-03 in CGI-RSK-001. Backups exist as CloudCo native snapshots but no restore has ever been tested and no RTO or RPO has been declared, so the company holds a backup but has never demonstrated a recovery capability; CGI-POL-006 Backup and Recovery was recommended in CGI-RSK-001 and has not been written (control gap CG-01). No policy in the CGI-POL-001 to CGI-POL-005 pack addresses cloud configuration at all, which is the documented reason R-005 remains at residual High.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-RSK-001 CG-01, CG-03; CGI-POL-006 recommended, not written; no CIS baseline or restore test evidence on file</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">R-002, R-005</t>
   </si>
   <si>
-    <t xml:space="preserve">R-005 (AWS misconfiguration leading to public data exposure) stays at residual 12, High, after treatment; a single permissive S3 or security group change exposes customer data with no baseline to deviate from and no posture monitoring to catch it.</t>
+    <t xml:space="preserve">R-005 (CloudCo misconfiguration leading to public data exposure) stays at residual 12, High, after treatment; a single permissive S3 or security group change exposes customer data with no baseline to deviate from and no posture monitoring to catch it.</t>
   </si>
   <si>
     <t xml:space="preserve">Apply a CIS AWS Foundations Benchmark baseline and enable continuous posture monitoring; publish CGI-POL-006 with declared RTO and RPO and evidence a successful restore test; document network segmentation and production access boundaries.</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">Assets are monitored to find anomalies, indicators of compromise and other potentially adverse events.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cypher Group Inc. has established the legal right to monitor without building the ability to do so. CGI-POL-001 §4.10 contains a properly drafted monitoring notice giving the company a lawful basis to inspect activity on its systems, but no monitoring capability exists behind it: AWS CloudTrail coverage and log file validation are unverified across regions, there is no centralised security log destination (engineering uses Datadog, CGI-VEN-007, for application performance monitoring, but it is not configured or retained as a security log source), no alerting on root account usage or IAM policy changes, no endpoint detection on the 50 staff devices and no monitoring of data egress from Google Workspace or GitHub. CGI-RSK-001 records the cloud half of this as control gap CG-03 (no drift detection) and the data-egress half as CG-05, and together they are the reason both R-003 and R-005 retain elevated residual positions - neither insider exfiltration nor a cloud misconfiguration would be observed as it occurred.</t>
+    <t xml:space="preserve">Cypher Group Inc. has established the legal right to monitor without building the ability to do so. CGI-POL-001 §4.10 contains a properly drafted monitoring notice giving the company a lawful basis to inspect activity on its systems, but no monitoring capability exists behind it: AWS CloudTrail coverage and log file validation are unverified across regions, there is no centralised security log destination (engineering uses MonitorCo, CGI-VEN-007, for application performance monitoring, but it is not configured or retained as a security log source), no alerting on root account usage or IAM policy changes, no endpoint detection on the 50 staff devices and no monitoring of data egress from OfficeCo or CodeCo. CGI-RSK-001 records the cloud half of this as control gap CG-03 (no drift detection) and the data-egress half as CG-05, and together they are the reason both R-003 and R-005 retain elevated residual positions - neither insider exfiltration nor a cloud misconfiguration would be observed as it occurred.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-POL-001 §4.10 (monitoring notice, no capability); CGI-RSK-001 CG-03, CG-05; no centralised logging on file</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">Anomalies, indicators of compromise and other potentially adverse events are analyzed to characterize the events and detect cybersecurity incidents.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-005 provides the classification half of this Category properly: SEV1 to SEV4 severity bands are defined with criteria, so an event that is reported would be triaged consistently against a written standard. Everything upstream of that is absent. There is no correlation of events across AWS, GitHub, Google Workspace and Slack, no alert thresholds, no defined escalation from an alert to a declared incident, and because DE.CM produces no telemetry there is nothing to analyse in the first place. In practice the only detection route available to Cypher Group Inc. is a human noticing something and reporting it through the CGI-POL-005 channel.</t>
+    <t xml:space="preserve">CGI-POL-005 provides the classification half of this Category properly: SEV1 to SEV4 severity bands are defined with criteria, so an event that is reported would be triaged consistently against a written standard. Everything upstream of that is absent. There is no correlation of events across CloudCo, CodeCo, OfficeCo and ChatCo, no alert thresholds, no defined escalation from an alert to a declared incident, and because DE.CM produces no telemetry there is nothing to analyse in the first place. In practice the only detection route available to Cypher Group Inc. is a human noticing something and reporting it through the CGI-POL-005 channel.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-POL-005 SEV1 to SEV4 definitions; CGI-RSK-001 CG-03, CG-05; no alerting or correlation on file</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">Breach scope cannot be established, so the company must either under-report and risk regulatory sanction or over-report and damage roughly 200 customer relationships unnecessarily.</t>
   </si>
   <si>
-    <t xml:space="preserve">Add an evidence collection and chain-of-custody procedure to CGI-POL-005 and define a minimum log retention period of twelve months for authentication, administrative and data access events across AWS, GitHub and Google Workspace.</t>
+    <t xml:space="preserve">Add an evidence collection and chain-of-custody procedure to CGI-POL-005 and define a minimum log retention period of twelve months for authentication, administrative and data access events across CloudCo, CodeCo and OfficeCo.</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.27 Learning from information security incidents; A.5.28 Collection of evidence; A.8.15 Logging</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">Activities are performed to prevent expansion of an event and mitigate its effects.</t>
   </si>
   <si>
-    <t xml:space="preserve">The one genuine containment capability Cypher Group Inc. has is the four-hour access revocation requirement in CGI-POL-003 §4.5.2, written for the leaver process rather than for incident response but usable in a credential compromise. CGI-POL-005 §5.5.1 names containment as a stage (disable accounts, rotate credentials, isolate systems) and CGI-POL-002 §4.5.3 requires a committed secret to be rotated, but nothing sits beneath those lines: there are no runbooks for isolating a compromised AWS resource, revoking active sessions or rotating credentials and secrets at speed, no anti-malware standard covering the 50 staff endpoints, and no pre-agreed authority for an engineer to take production action without approval during a live incident. Containment would therefore be improvised under pressure by whoever holds AWS credentials. The policy states what containment is but not how to do it, so the Category is scored down to 1.</t>
+    <t xml:space="preserve">The one genuine containment capability Cypher Group Inc. has is the four-hour access revocation requirement in CGI-POL-003 §4.5.2, written for the leaver process rather than for incident response but usable in a credential compromise. CGI-POL-005 §5.5.1 names containment as a stage (disable accounts, rotate credentials, isolate systems) and CGI-POL-002 §4.5.3 requires a committed secret to be rotated, but nothing sits beneath those lines: there are no runbooks for isolating a compromised CloudCo resource, revoking active sessions or rotating credentials and secrets at speed, no anti-malware standard covering the 50 staff endpoints, and no pre-agreed authority for an engineer to take production action without approval during a live incident. Containment would therefore be improvised under pressure by whoever holds CloudCo credentials. The policy states what containment is but not how to do it, so the Category is scored down to 1.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-POL-003 §4.5.2; CGI-POL-005 §5.5.1; CGI-POL-002 §4.5.3 (no rotation runbook); no containment runbooks on file</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">Restoration activities are performed to ensure operational availability of systems and services affected by cybersecurity incidents.</t>
   </si>
   <si>
-    <t xml:space="preserve">Backups exist as AWS native snapshots, which is why this Category scores 1 rather than 0, but no restore has ever been tested, no recovery time objective or recovery point objective has been declared, no recovery plan document exists and no recovery roles have been assigned. CGI-POL-006 Backup and Recovery was identified as necessary in CGI-RSK-001 and has not been written, and the absence of tested recovery is control gap CG-01. An untested backup is not a recovery capability, it is an assumption - which is why CGI-RSK-001 deliberately gives R-002 no credit for backups and holds its residual impact at 4 until CG-01 is closed. This assessment reaches the same conclusion from the other direction.</t>
+    <t xml:space="preserve">Backups exist as CloudCo native snapshots, which is why this Category scores 1 rather than 0, but no restore has ever been tested, no recovery time objective or recovery point objective has been declared, no recovery plan document exists and no recovery roles have been assigned. CGI-POL-006 Backup and Recovery was identified as necessary in CGI-RSK-001 and has not been written, and the absence of tested recovery is control gap CG-01. An untested backup is not a recovery capability, it is an assumption - which is why CGI-RSK-001 deliberately gives R-002 no credit for backups and holds its residual impact at 4 until CG-01 is closed. This assessment reaches the same conclusion from the other direction.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-RSK-001 CG-01 and R-002 residual rationale; CGI-POL-006 recommended, not written; no restore test record on file</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">REC-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Build an asset and SaaS inventory covering AWS accounts and data stores, GitHub repositories, Google Workspace shared drives, Slack workspaces, Stripe objects and staff endpoints, labelled per CGI-POL-004.</t>
+    <t xml:space="preserve">Build an asset and SaaS inventory covering CloudCo accounts and data stores, CodeCo repositories, OfficeCo shared drives, ChatCo workspaces, PaymentsCo objects and staff endpoints, labelled per CGI-POL-004.</t>
   </si>
   <si>
     <t xml:space="preserve">R-003, R-005; ID.AM maturity 1 to 2</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">REC-06</t>
   </si>
   <si>
-    <t xml:space="preserve">Publish CGI-POL-007 Secure Development and Change Management and enforce GitHub branch protection with mandatory peer review and no direct commits to main.</t>
+    <t xml:space="preserve">Publish CGI-POL-007 Secure Development and Change Management and enforce CodeCo branch protection with mandatory peer review and no direct commits to main.</t>
   </si>
   <si>
     <t xml:space="preserve">R-004; CG-02</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">REC-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Apply a CIS AWS Foundations Benchmark baseline and enable continuous cloud security posture monitoring across all AWS accounts.</t>
+    <t xml:space="preserve">Apply a CIS AWS Foundations Benchmark baseline and enable continuous cloud security posture monitoring across all CloudCo accounts.</t>
   </si>
   <si>
     <t xml:space="preserve">R-005; CG-03</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">REC-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Build a tiered vendor inventory for AWS, GitHub, Slack, Google Workspace and Stripe with assurance artifacts and DPAs, and add permitted third-party destinations to CGI-POL-004 s4.2.</t>
+    <t xml:space="preserve">Build a tiered vendor inventory for CloudCo, CodeCo, ChatCo, OfficeCo and PaymentsCo with assurance artifacts and DPAs, and add permitted third-party destinations to CGI-POL-004 s4.2.</t>
   </si>
   <si>
     <t xml:space="preserve">GV.SC maturity 0 to 2; R-005 (adjacent)</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">REC-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Deploy data egress and data loss prevention monitoring on Google Workspace and GitHub covering mass download, external sharing and repository cloning by departing staff.</t>
+    <t xml:space="preserve">Deploy data egress and data loss prevention monitoring on OfficeCo and CodeCo covering mass download, external sharing and repository cloning by departing staff.</t>
   </si>
   <si>
     <t xml:space="preserve">R-003; CG-05</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">REC-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Document network segmentation, production access boundaries and the shared responsibility boundary between AWS and Cypher Group Inc.</t>
+    <t xml:space="preserve">Document network segmentation, production access boundaries and the shared responsibility boundary between CloudCo and Cypher Group Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">R-004, R-005; PR.IR maturity</t>
@@ -2669,176 +2669,258 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-GAP-001 — NIST CSF 2.0 Gap Assessment &amp; Maturity Scorecard v1.0</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIMULATED CASE STUDY. Cypher Group Inc. is a simulated company. Every finding, score and figure was created to demonstrate applied GRC methodology.</t>
+        </is>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scope</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All 22 NIST CSF 2.0 Categories across 6 Functions, Category level. Secondary mapping: ISO/IEC 27001:2022 Annex A.</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scale</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0–4 CMMI-style maturity. An approved but unevidenced policy is a 2, never a 3. A clause is not a capability (fragment rule).</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prepared by</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O.S, Assessor</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved by</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer — 15 September 2026</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>11</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inputs</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-POL-001 to 005 · CGI-TRK-001 · EXC-001 to 003 · CGI-RSK-001 v1.0</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>12</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHEETS</t>
+        </is>
       </c>
       <c r="B10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01_Maturity_Scale</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 0–4 scale, the fragment rule and the declared target state.</t>
+        </is>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>16</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02_Assessment</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 16-column grid for all 22 Categories. Scores are yellow inputs with 0–4 validation; Gap is a formula; colour scales are pinned to numbers.</t>
+        </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03_Heatmap</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Function averages via AVERAGEIF, the overall score as the mean of all 22 Categories, and the current-vs-target radar chart.</t>
+        </is>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>20</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04_Roadmap</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REC-01 to REC-18. Reduction per effort unit is a formula (S=1, M=2, L=3).</t>
+        </is>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>22</v>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05_Consistency_Checks</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live checks: category count, sums, no target below current, fragment and residual-High reconciliation.</t>
+        </is>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>24</v>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06_Issue_Checklist</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality checks performed before issue.</t>
+        </is>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>25</v>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLOUR LEGEND</t>
+        </is>
       </c>
       <c r="B18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>27</v>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yellow cell</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input — type or choose here</t>
+        </is>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>29</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grey cell</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula — do not overwrite</t>
+        </is>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>31</v>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass / compliant / low</t>
+        </is>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>33</v>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amber</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial / condition / medium</t>
+        </is>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>35</v>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fail / non-compliant / high or critical</t>
+        </is>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>36</v>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHING</t>
+        </is>
       </c>
       <c r="B25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>38</v>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitHub</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload this .xlsx next to its .md file. GitHub cannot preview .xlsx, so the project README links to it as a download.</t>
+        </is>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>40</v>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notion</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import the matching CSV files from the data/ folder (Settings → Import → CSV) for sortable databases.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
+++ b/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
@@ -707,7 +707,7 @@
     <t xml:space="preserve">Security architectures are managed with the organization's risk strategy to protect asset confidentiality, integrity and availability, and organizational resilience.</t>
   </si>
   <si>
-    <t xml:space="preserve">This Category also scores zero. There is no documented CloudCo configuration baseline, no benchmark such as CIS CloudCo Foundations has been applied, no continuous cloud security posture monitoring is enabled, and no network segmentation or production access boundary is recorded anywhere - collectively control gap CG-03 in CGI-RSK-001. Backups exist as CloudCo native snapshots but no restore has ever been tested and no RTO or RPO has been declared, so the company holds a backup but has never demonstrated a recovery capability; CGI-POL-006 Backup and Recovery was recommended in CGI-RSK-001 and has not been written (control gap CG-01). No policy in the CGI-POL-001 to CGI-POL-005 pack addresses cloud configuration at all, which is the documented reason R-005 remains at residual High.</t>
+    <t xml:space="preserve">This Category also scores zero. There is no documented CloudCo configuration baseline, no benchmark such as CIS AWS Foundations has been applied, no continuous cloud security posture monitoring is enabled, and no network segmentation or production access boundary is recorded anywhere - collectively control gap CG-03 in CGI-RSK-001. Backups exist as CloudCo native snapshots but no restore has ever been tested and no RTO or RPO has been declared, so the company holds a backup but has never demonstrated a recovery capability; CGI-POL-006 Backup and Recovery was recommended in CGI-RSK-001 and has not been written (control gap CG-01). No policy in the CGI-POL-001 to CGI-POL-005 pack addresses cloud configuration at all, which is the documented reason R-005 remains at residual High.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-RSK-001 CG-01, CG-03; CGI-POL-006 recommended, not written; no CIS baseline or restore test evidence on file</t>

--- a/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
+++ b/03-nist-csf-gap-assessment/03-nist-csf-gap-assessment.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">Approved by</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer — 15 September 2026</t>
+    <t xml:space="preserve">Jerry Gold, Chief Executive Officer — 15 September 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Inputs</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">Organizational cybersecurity policy is established, communicated and enforced.</t>
   </si>
   <si>
-    <t xml:space="preserve">This is the company's strongest documented area and the direct output of Project 1: CGI-POL-001 to CGI-POL-005 v1.0 are written, approved by Jerry Olugboye and published, covering acceptable use, password and MFA, joiner-mover-leaver access control, data classification and incident reporting, with an Exception Register carrying EXC-001 to EXC-003. Enforcement is the gap, not authorship. CGI-TRK-001 evidences only 60% policy acknowledgement across 50 employees, meaning roughly 20 staff are bound by policies they have not read; the annual review cycle mandated in each policy's document control block has not yet run once, so no policy has a demonstrated review record. Three policies identified as necessary in CGI-RSK-001 - CGI-POL-006 Backup and Recovery, CGI-POL-007 Secure Development and Change Management and CGI-POL-008 Vulnerability Management - remain unwritten.</t>
+    <t xml:space="preserve">This is the company's strongest documented area and the direct output of Project 1: CGI-POL-001 to CGI-POL-005 v1.0 are written, approved by Jerry Gold and published, covering acceptable use, password and MFA, joiner-mover-leaver access control, data classification and incident reporting, with an Exception Register carrying EXC-001 to EXC-003. Enforcement is the gap, not authorship. CGI-TRK-001 evidences only 60% policy acknowledgement across 50 employees, meaning roughly 20 staff are bound by policies they have not read; the annual review cycle mandated in each policy's document control block has not yet run once, so no policy has a demonstrated review record. Three policies identified as necessary in CGI-RSK-001 - CGI-POL-006 Backup and Recovery, CGI-POL-007 Secure Development and Change Management and CGI-POL-008 Vulnerability Management - remain unwritten.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-POL-001 to CGI-POL-005 v1.0; CGI-TRK-001 (60% acknowledged); EXC-001 to EXC-003; CGI-RSK-001 recommended policies</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">Results of organization-wide cybersecurity risk management activities and performance are used to inform, improve and adjust the risk management strategy.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-RSK-001 defines seven Key Risk Indicators with thresholds and named owners, which is the raw material for oversight, but not one of them has ever been measured or reported; no management review of the security programme has taken place, and no security item has appeared on a leadership agenda with minutes. The 52% inherent-to-residual risk reduction attributable to the Project 1 policy pack (aggregate 92 to 44, mean 18.4 to 8.8) is a strong, defensible performance figure that has never been presented to Jerry Olugboye, so leadership has no basis on which to adjust strategy or release the USD 32,100 budget.</t>
+    <t xml:space="preserve">CGI-RSK-001 defines seven Key Risk Indicators with thresholds and named owners, which is the raw material for oversight, but not one of them has ever been measured or reported; no management review of the security programme has taken place, and no security item has appeared on a leadership agenda with minutes. The 52% inherent-to-residual risk reduction attributable to the Project 1 policy pack (aggregate 92 to 44, mean 18.4 to 8.8) is a strong, defensible performance figure that has never been presented to Jerry Gold, so leadership has no basis on which to adjust strategy or release the USD 32,100 budget.</t>
   </si>
   <si>
     <t xml:space="preserve">CGI-RSK-001 KRI table (7 KRIs, unreported); no management review minutes on file</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">Leadership cannot fund, redirect or defend a programme whose performance it never sees, so security investment competes on anecdote rather than evidence.</t>
   </si>
   <si>
-    <t xml:space="preserve">Establish a minuted quarterly security review with Jerry Olugboye reporting the seven CGI-RSK-001 KRIs, this maturity scorecard and TP-01 to TP-10 status; retain the minutes as the oversight evidence record.</t>
+    <t xml:space="preserve">Establish a minuted quarterly security review with Jerry Gold reporting the seven CGI-RSK-001 KRIs, this maturity scorecard and TP-01 to TP-10 status; retain the minutes as the oversight evidence record.</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.35 Independent review of information security; A.5.36 Compliance with policies, rules and standards (supports Clause 9.3 Management review)</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">The cybersecurity risk to the organization, assets and individuals is understood by the organization.</t>
   </si>
   <si>
-    <t xml:space="preserve">This is the only Category at Cypher Group Inc. that demonstrates both design and operating effectiveness. CGI-RSK-001 v1.0 was performed end to end using NIST SP 800-30 Rev. 1, documents five scenarios (R-001 to R-005) in full threat-source to business-consequence form, records both inherent (20/20/12/20/20) and residual (6/8/6/12/12) scores, cites a specific CGI-POL clause for every mitigating control across more than 60 clause-level cross-references, applies all four treatment strategies including a formally documented acceptance and avoidance, and was approved by Jerry Olugboye. It is scored 3 rather than 4 because no metrics govern the process and because the identification input is incomplete: CSF Subcategory ID.RA-01 requires vulnerabilities in assets to be identified, and Cypher Group Inc. performs no vulnerability scanning of any kind (control gap CG-02), so the register's coverage rests on workshop judgement rather than on technical discovery.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGI-RSK-001 v1.0 (approved, Jerry Olugboye); R-001 to R-005; CG-01 to CG-05; TP-01 to TP-10</t>
+    <t xml:space="preserve">This is the only Category at Cypher Group Inc. that demonstrates both design and operating effectiveness. CGI-RSK-001 v1.0 was performed end to end using NIST SP 800-30 Rev. 1, documents five scenarios (R-001 to R-005) in full threat-source to business-consequence form, records both inherent (20/20/12/20/20) and residual (6/8/6/12/12) scores, cites a specific CGI-POL clause for every mitigating control across more than 60 clause-level cross-references, applies all four treatment strategies including a formally documented acceptance and avoidance, and was approved by Jerry Gold. It is scored 3 rather than 4 because no metrics govern the process and because the identification input is incomplete: CSF Subcategory ID.RA-01 requires vulnerabilities in assets to be identified, and Cypher Group Inc. performs no vulnerability scanning of any kind (control gap CG-02), so the register's coverage rests on workshop judgement rather than on technical discovery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGI-RSK-001 v1.0 (approved, Jerry Gold); R-001 to R-005; CG-01 to CG-05; TP-01 to TP-10</t>
   </si>
   <si>
     <t xml:space="preserve">R-001, R-002, R-003, R-004, R-005</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">In a ransomware event the company would discover whether its backups restore at the worst possible moment, and an unrecoverable SaaS platform is an existential rather than a financial event for roughly 200 customers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Perform and document a full restore test to a clean environment, publish CGI-POL-006 with declared RTO and RPO approved by Jerry Olugboye, and schedule the restore test to repeat every six months as a KRI.</t>
+    <t xml:space="preserve">Perform and document a full restore test to a clean environment, publish CGI-POL-006 with declared RTO and RPO approved by Jerry Gold, and schedule the restore test to repeat every six months as a KRI.</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.29 Information security during disruption; A.5.30 ICT readiness for business continuity; A.8.13 Information backup</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">REC-03</t>
   </si>
   <si>
-    <t xml:space="preserve">Perform and document a full backup restore test to a clean environment, then publish CGI-POL-006 Backup and Recovery with RTO and RPO approved by Jerry Olugboye.</t>
+    <t xml:space="preserve">Perform and document a full backup restore test to a clean environment, then publish CGI-POL-006 Backup and Recovery with RTO and RPO approved by Jerry Gold.</t>
   </si>
   <si>
     <t xml:space="preserve">R-002; CG-01</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">REC-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Establish a minuted quarterly security review with Jerry Olugboye reporting the seven CGI-RSK-001 KRIs, this maturity scorecard and TP-01 to TP-10 status.</t>
+    <t xml:space="preserve">Establish a minuted quarterly security review with Jerry Gold reporting the seven CGI-RSK-001 KRIs, this maturity scorecard and TP-01 to TP-10 status.</t>
   </si>
   <si>
     <t xml:space="preserve">GV.OV maturity 1 to 2</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer — 15 September 2026</t>
+          <t xml:space="preserve">Jerry Gold, Chief Executive Officer — 15 September 2026</t>
         </is>
       </c>
     </row>
